--- a/onlineCompcorImplementation/results/allDatasetMean.xlsx
+++ b/onlineCompcorImplementation/results/allDatasetMean.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/ironanMain/workFiles/phDWork/realDataAnalysis/realData/onlineCompcorImplementation/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE86CDC0-D766-5647-9D94-7BF2326FAE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B1738D-BA67-624B-80BF-05875FE67582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1800" yWindow="600" windowWidth="27000" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9B6"/>
+        <fgColor rgb="FFFFFBC7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -140,7 +140,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFF9B6"/>
+      <color rgb="FFFFFBC7"/>
     </mruColors>
   </colors>
   <extLst>
@@ -706,7 +706,7 @@
   </sheetData>
   <autoFilter ref="A1:G11" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G11">
-      <sortCondition descending="1" ref="G2:G11"/>
+      <sortCondition descending="1" ref="G1:G11"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
